--- a/Employees Email id.xlsx
+++ b/Employees Email id.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="114">
   <si>
     <t>Mayur Kumar</t>
   </si>
@@ -98,7 +98,7 @@
     <t>Sakshi Sharma</t>
   </si>
   <si>
-    <t>Ravneet Kaur</t>
+    <t>Shouvik Dey</t>
   </si>
   <si>
     <t>Vineet Kumar</t>
@@ -369,6 +369,12 @@
   </si>
   <si>
     <t>amanjot.singh@caglobal.com</t>
+  </si>
+  <si>
+    <t>Baby Jangra</t>
+  </si>
+  <si>
+    <t>baby.jangra@caglobal.com</t>
   </si>
 </sst>
 </file>
@@ -1088,10 +1094,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="2" t="s">
-        <v>105</v>
+        <v>24</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C27">
         <v>2</v>
@@ -1099,10 +1105,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C28">
         <v>2</v>
@@ -1110,10 +1116,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C29">
         <v>2</v>
@@ -1121,10 +1127,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C30">
         <v>2</v>
@@ -1132,10 +1138,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C31">
         <v>2</v>
@@ -1143,10 +1149,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C32">
         <v>2</v>
@@ -1154,10 +1160,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C33">
         <v>2</v>
@@ -1165,10 +1171,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C34">
         <v>2</v>
@@ -1176,10 +1182,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C35">
         <v>2</v>
@@ -1187,10 +1193,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C36">
         <v>2</v>
@@ -1198,10 +1204,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C37">
         <v>2</v>
@@ -1209,10 +1215,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C38">
         <v>2</v>
@@ -1220,10 +1226,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C39">
         <v>2</v>
@@ -1231,10 +1237,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="2" t="s">
-        <v>36</v>
+        <v>103</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C40">
         <v>2</v>
@@ -1242,10 +1248,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C41">
         <v>2</v>
@@ -1253,10 +1259,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="2" t="s">
-        <v>104</v>
+        <v>37</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C42">
         <v>2</v>
@@ -1264,10 +1270,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="2" t="s">
-        <v>37</v>
+        <v>80</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C43">
         <v>2</v>
@@ -1275,10 +1281,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C44">
         <v>2</v>
@@ -1286,10 +1292,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>93</v>
       </c>
       <c r="C45">
         <v>2</v>
@@ -1297,10 +1303,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C46">
         <v>2</v>
@@ -1308,10 +1314,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C47">
         <v>2</v>
@@ -1319,10 +1325,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C48">
         <v>2</v>
@@ -1330,10 +1336,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C49">
         <v>2</v>
@@ -1341,10 +1347,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C50">
         <v>2</v>
@@ -1352,10 +1358,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C51">
         <v>2</v>
@@ -1363,21 +1369,21 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C52">
         <v>2</v>
       </c>
     </row>
     <row r="53" spans="1:3">
-      <c r="A53" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>99</v>
+      <c r="A53" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>109</v>
       </c>
       <c r="C53">
         <v>2</v>
@@ -1385,26 +1391,35 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
+      </c>
+      <c r="C54">
+        <v>2</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
+      </c>
+      <c r="C55">
+        <v>2</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" s="1" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>111</v>
+        <v>113</v>
+      </c>
+      <c r="C56">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -1435,34 +1450,54 @@
     <hyperlink ref="B24" r:id="rId23"/>
     <hyperlink ref="B25" r:id="rId24"/>
     <hyperlink ref="B26" r:id="rId25"/>
-    <hyperlink ref="B27" r:id="rId26"/>
-    <hyperlink ref="B28" r:id="rId27"/>
-    <hyperlink ref="B29" r:id="rId28"/>
-    <hyperlink ref="B30" r:id="rId29"/>
-    <hyperlink ref="B31" r:id="rId30"/>
-    <hyperlink ref="B32" r:id="rId31"/>
-    <hyperlink ref="B33" r:id="rId32"/>
-    <hyperlink ref="B34" r:id="rId33"/>
-    <hyperlink ref="B35" r:id="rId34"/>
-    <hyperlink ref="B36" r:id="rId35"/>
-    <hyperlink ref="B37" r:id="rId36"/>
-    <hyperlink ref="B38" r:id="rId37"/>
-    <hyperlink ref="B39" r:id="rId38"/>
-    <hyperlink ref="B40" r:id="rId39"/>
-    <hyperlink ref="B41" r:id="rId40"/>
-    <hyperlink ref="B42" r:id="rId41"/>
-    <hyperlink ref="B43" r:id="rId42"/>
-    <hyperlink ref="B44" r:id="rId43"/>
-    <hyperlink ref="B45" r:id="rId44"/>
-    <hyperlink ref="B54" r:id="rId45"/>
-    <hyperlink ref="B55" r:id="rId46"/>
-    <hyperlink ref="B56" r:id="rId47"/>
+    <hyperlink ref="B27" r:id="rId27"/>
+    <hyperlink ref="B27" r:id="rId28"/>
+    <hyperlink ref="B27" r:id="rId29"/>
+    <hyperlink ref="B27" r:id="rId30"/>
+    <hyperlink ref="B27" r:id="rId31"/>
+    <hyperlink ref="B27" r:id="rId32"/>
+    <hyperlink ref="B27" r:id="rId33"/>
+    <hyperlink ref="B27" r:id="rId34"/>
+    <hyperlink ref="B27" r:id="rId35"/>
+    <hyperlink ref="B27" r:id="rId36"/>
+    <hyperlink ref="B27" r:id="rId37"/>
+    <hyperlink ref="B27" r:id="rId38"/>
+    <hyperlink ref="B27" r:id="rId39"/>
+    <hyperlink ref="B27" r:id="rId40"/>
+    <hyperlink ref="B27" r:id="rId41"/>
+    <hyperlink ref="B27" r:id="rId42"/>
+    <hyperlink ref="B27" r:id="rId43"/>
+    <hyperlink ref="B27" r:id="rId44"/>
+    <hyperlink ref="B27" r:id="rId45"/>
+    <hyperlink ref="B27" r:id="rId46"/>
+    <hyperlink ref="B27" r:id="rId47"/>
+    <hyperlink ref="B27" r:id="rId48"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="84bad432-a1f2-42cb-8756-b2f1877d4a9a" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3e99dead-b236-4fab-aee5-fd8bc6997613">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101007927F4694DDC484DB27E1F1CB233C398" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="839fee7d02049c8e712e1552656fdb70">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3e99dead-b236-4fab-aee5-fd8bc6997613" xmlns:ns3="84bad432-a1f2-42cb-8756-b2f1877d4a9a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="aa1ecd4ba7e10c12d4a8901a622c9c64" ns2:_="" ns3:_="">
     <xsd:import namespace="3e99dead-b236-4fab-aee5-fd8bc6997613"/>
@@ -1697,27 +1732,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A21C65C9-7483-4532-AD73-B2E541DB4E00}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="84bad432-a1f2-42cb-8756-b2f1877d4a9a"/>
+    <ds:schemaRef ds:uri="3e99dead-b236-4fab-aee5-fd8bc6997613"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="84bad432-a1f2-42cb-8756-b2f1877d4a9a" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3e99dead-b236-4fab-aee5-fd8bc6997613">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BB7F88CD-C1F3-4A57-A030-D78A840BF87D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7FE907E5-9621-46CB-B265-2AF8DFD3C810}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1734,23 +1768,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BB7F88CD-C1F3-4A57-A030-D78A840BF87D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A21C65C9-7483-4532-AD73-B2E541DB4E00}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="84bad432-a1f2-42cb-8756-b2f1877d4a9a"/>
-    <ds:schemaRef ds:uri="3e99dead-b236-4fab-aee5-fd8bc6997613"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>